--- a/Data/訂單相關資料表.xlsx
+++ b/Data/訂單相關資料表.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ImportDataToERP\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7A0138-A2C7-4B92-92BB-023FA93C032E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5D6001-FBD0-422C-A505-7264F2BB6488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8D52DE2C-1782-4129-9156-D6E11B79C1B3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D52DE2C-1782-4129-9156-D6E11B79C1B3}"/>
   </bookViews>
   <sheets>
     <sheet name="訂單相關資料表" sheetId="1" r:id="rId1"/>
     <sheet name="品號主檔" sheetId="5" r:id="rId2"/>
-    <sheet name="公司別資料表" sheetId="2" r:id="rId3"/>
-    <sheet name="客戶資料表" sheetId="3" r:id="rId4"/>
-    <sheet name="單據性質資料表" sheetId="4" r:id="rId5"/>
+    <sheet name="庫別" sheetId="6" r:id="rId3"/>
+    <sheet name="工作表2" sheetId="7" r:id="rId4"/>
+    <sheet name="公司別資料表" sheetId="2" r:id="rId5"/>
+    <sheet name="客戶資料表" sheetId="3" r:id="rId6"/>
+    <sheet name="單據性質資料表" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5314" uniqueCount="2291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5448" uniqueCount="2339">
   <si>
     <t xml:space="preserve">COPTC     </t>
   </si>
@@ -6924,6 +6926,150 @@
   </si>
   <si>
     <t>特性45      //951004 S00-9510009 GP1.0 ADD ↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVMC     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">品號庫別檔                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC001          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC002          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC003          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">儲存位置                                    </t>
+  </si>
+  <si>
+    <t>儲位   //941108 MODI 儲位--&gt;儲存位置 S00-9410022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC004          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">安全存量                                    </t>
+  </si>
+  <si>
+    <t>安全存量//950808 S00-9508031 N11.3-&gt;N16.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC005          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">補貨點                                     </t>
+  </si>
+  <si>
+    <t>補貨點//950808 S00-9508031 N11.3-&gt;N16.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC006          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">經濟批量                                    </t>
+  </si>
+  <si>
+    <t>經濟批量//950808 S00-9508031 N11.3-&gt;N16.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC007          </t>
+  </si>
+  <si>
+    <t>庫存數量//950808 S00-9508031 N12.3-&gt;N16.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC008          </t>
+  </si>
+  <si>
+    <t>庫存金額//950808 S00-9508031 N14.2-&gt;N21.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC009          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">標準存貨量                                   </t>
+  </si>
+  <si>
+    <t>標準存貨量//950808 S00-9508031 N12.3-&gt;N16.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC010          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">標準週轉率                                   </t>
+  </si>
+  <si>
+    <t>標準週轉率 //950808 S00-9508031 N5.4-&gt;N8.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC011          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">上次盤點日                                   </t>
+  </si>
+  <si>
+    <t>上次盤點日[FORMATE:YMD]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC012          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">最近入庫日                                   </t>
+  </si>
+  <si>
+    <t>最近入庫日[FORMATE:YMD]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC013          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">最近出庫日                                   </t>
+  </si>
+  <si>
+    <t>最近出庫日[FORMATE:YMD]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC014          </t>
+  </si>
+  <si>
+    <t>庫存包裝數量 &amp;&amp;890921 ADD BY 862//950808 S00-9508031 N12.3-&gt;N16.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC015          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">主要儲位                                    </t>
+  </si>
+  <si>
+    <t>主要儲位  //941108 7.1 ADD S00-9410022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC016          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC017          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC018          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC019          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC020          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC200          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">品號庫別備註                                  </t>
+  </si>
+  <si>
+    <t>品號庫別備註          //1259_002 MODI ^_^</t>
   </si>
 </sst>
 </file>
@@ -24975,6 +25121,609 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F74F2C6-2FCB-460E-8481-A3E672525D19}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="77.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2293</v>
+      </c>
+      <c r="E2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2296</v>
+      </c>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2299</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>16.3</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>16.3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>16.3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E8" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>16.3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1773</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>21.6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2311</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2312</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>16.3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2315</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>8.5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2321</v>
+      </c>
+      <c r="F13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2323</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2324</v>
+      </c>
+      <c r="F14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>16.3</v>
+      </c>
+      <c r="H15" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2329</v>
+      </c>
+      <c r="F16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2331</v>
+      </c>
+      <c r="E17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>21.6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18">
+        <v>15.6</v>
+      </c>
+      <c r="H18" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2334</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>30</v>
+      </c>
+      <c r="H20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>60</v>
+      </c>
+      <c r="H21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C22">
+        <v>200</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2337</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22">
+        <v>255</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10E51C0-3CAA-4B55-8198-270A0C8836E7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{534A4AFF-42BF-43FD-B28B-BF7EC6FC552B}">
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -25307,7 +26056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4004A585-AA21-45B3-865B-306C96B191B5}">
   <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -28552,7 +29301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0763CD0-2084-4B20-9A0C-2B0E6D6BAEEA}">
   <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
